--- a/database/event/5279/event_5279_evp_summary.xlsx
+++ b/database/event/5279/event_5279_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>1.6843</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9954</v>
+        <v>2.9256</v>
       </c>
       <c r="E2" t="n">
         <v>8.457700000000001</v>
@@ -548,7 +548,7 @@
         <v>1.3804</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3788</v>
+        <v>2.3176</v>
       </c>
       <c r="E3" t="n">
         <v>6.9315</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.8503</v>
+        <v>6.8209</v>
       </c>
       <c r="C4" t="n">
-        <v>1.3642</v>
+        <v>1.3583</v>
       </c>
       <c r="D4" t="n">
-        <v>2.346</v>
+        <v>2.2735</v>
       </c>
       <c r="E4" t="n">
-        <v>6.8503</v>
+        <v>6.8209</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9545</v>
+        <v>3.9251</v>
       </c>
       <c r="G4" t="n">
         <v>2.8958</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9545</v>
+        <v>3.9251</v>
       </c>
       <c r="I4" t="n">
         <v>3.9914</v>
@@ -640,7 +640,7 @@
         <v>1.3229</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2623</v>
+        <v>2.2027</v>
       </c>
       <c r="E5" t="n">
         <v>6.6431</v>
@@ -686,7 +686,7 @@
         <v>1.307</v>
       </c>
       <c r="D6" t="n">
-        <v>2.23</v>
+        <v>2.1708</v>
       </c>
       <c r="E6" t="n">
         <v>6.5631</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5.8667</v>
+        <v>5.8406</v>
       </c>
       <c r="C7" t="n">
-        <v>1.1683</v>
+        <v>1.1631</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9487</v>
+        <v>1.883</v>
       </c>
       <c r="E7" t="n">
-        <v>5.8667</v>
+        <v>5.8406</v>
       </c>
       <c r="F7" t="n">
-        <v>4.9824</v>
+        <v>4.9563</v>
       </c>
       <c r="G7" t="n">
         <v>0.8843</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5094</v>
+        <v>5.4684</v>
       </c>
       <c r="I7" t="n">
         <v>5.5608</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>KSCERATO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.8284</v>
+        <v>5.8109</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1607</v>
+        <v>1.1572</v>
       </c>
       <c r="D8" t="n">
-        <v>1.9332</v>
+        <v>1.8712</v>
       </c>
       <c r="E8" t="n">
-        <v>5.8284</v>
+        <v>5.8109</v>
       </c>
       <c r="F8" t="n">
-        <v>5.2097</v>
+        <v>4.8663</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6187</v>
+        <v>0.9446</v>
       </c>
       <c r="H8" t="n">
-        <v>5.8658</v>
+        <v>11.0282</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9481</v>
+        <v>8.938700000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6187</v>
+        <v>0.9446</v>
       </c>
       <c r="K8" t="n">
-        <v>434</v>
+        <v>330</v>
       </c>
       <c r="L8" t="n">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="M8" t="n">
-        <v>6.566800000000001</v>
+        <v>9.8833</v>
       </c>
       <c r="N8" t="n">
-        <v>520</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KSCERATO</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.8109</v>
+        <v>5.7867</v>
       </c>
       <c r="C9" t="n">
-        <v>1.1572</v>
+        <v>1.1524</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9261</v>
+        <v>1.8615</v>
       </c>
       <c r="E9" t="n">
-        <v>5.8109</v>
+        <v>5.7867</v>
       </c>
       <c r="F9" t="n">
-        <v>4.8663</v>
+        <v>5.168</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9446</v>
+        <v>0.6187</v>
       </c>
       <c r="H9" t="n">
-        <v>11.0282</v>
+        <v>5.8004</v>
       </c>
       <c r="I9" t="n">
-        <v>8.938700000000001</v>
+        <v>5.9481</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9446</v>
+        <v>0.6187</v>
       </c>
       <c r="K9" t="n">
-        <v>330</v>
+        <v>434</v>
       </c>
       <c r="L9" t="n">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="M9" t="n">
-        <v>9.8833</v>
+        <v>6.566800000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>463</v>
+        <v>520</v>
       </c>
     </row>
     <row r="10">
@@ -870,7 +870,7 @@
         <v>1.0954</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8006</v>
+        <v>1.7474</v>
       </c>
       <c r="E10" t="n">
         <v>5.5003</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.4731</v>
+        <v>5.4305</v>
       </c>
       <c r="C11" t="n">
-        <v>1.0899</v>
+        <v>1.0815</v>
       </c>
       <c r="D11" t="n">
-        <v>1.7896</v>
+        <v>1.7196</v>
       </c>
       <c r="E11" t="n">
-        <v>5.4731</v>
+        <v>5.4305</v>
       </c>
       <c r="F11" t="n">
-        <v>5.2961</v>
+        <v>5.2535</v>
       </c>
       <c r="G11" t="n">
         <v>0.177</v>
       </c>
       <c r="H11" t="n">
-        <v>6.0013</v>
+        <v>5.9344</v>
       </c>
       <c r="I11" t="n">
         <v>6.0855</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5.1274</v>
+        <v>5.1064</v>
       </c>
       <c r="C12" t="n">
-        <v>1.0211</v>
+        <v>1.0169</v>
       </c>
       <c r="D12" t="n">
-        <v>1.65</v>
+        <v>1.5905</v>
       </c>
       <c r="E12" t="n">
-        <v>5.1274</v>
+        <v>5.1064</v>
       </c>
       <c r="F12" t="n">
-        <v>4.2957</v>
+        <v>4.2747</v>
       </c>
       <c r="G12" t="n">
         <v>0.8317</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4326</v>
+        <v>4.3996</v>
       </c>
       <c r="I12" t="n">
         <v>4.474</v>
@@ -1008,7 +1008,7 @@
         <v>1.0089</v>
       </c>
       <c r="D13" t="n">
-        <v>1.6252</v>
+        <v>1.5744</v>
       </c>
       <c r="E13" t="n">
         <v>5.0661</v>
@@ -1054,7 +1054,7 @@
         <v>0.9709</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5481</v>
+        <v>1.4984</v>
       </c>
       <c r="E14" t="n">
         <v>4.8752</v>
@@ -1100,7 +1100,7 @@
         <v>0.8894</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3828</v>
+        <v>1.3353</v>
       </c>
       <c r="E15" t="n">
         <v>4.466</v>
@@ -1146,7 +1146,7 @@
         <v>0.8691</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3416</v>
+        <v>1.2947</v>
       </c>
       <c r="E16" t="n">
         <v>4.3641</v>
@@ -1192,7 +1192,7 @@
         <v>0.8447</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2921</v>
+        <v>1.2459</v>
       </c>
       <c r="E17" t="n">
         <v>4.2414</v>
@@ -1238,7 +1238,7 @@
         <v>0.8295</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2613</v>
+        <v>1.2155</v>
       </c>
       <c r="E18" t="n">
         <v>4.1652</v>
@@ -1284,7 +1284,7 @@
         <v>0.8091</v>
       </c>
       <c r="D19" t="n">
-        <v>1.22</v>
+        <v>1.1748</v>
       </c>
       <c r="E19" t="n">
         <v>4.063</v>
@@ -1330,7 +1330,7 @@
         <v>0.7317</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0629</v>
+        <v>1.0198</v>
       </c>
       <c r="E20" t="n">
         <v>3.674</v>
@@ -1376,7 +1376,7 @@
         <v>0.728</v>
       </c>
       <c r="D21" t="n">
-        <v>1.0555</v>
+        <v>1.0126</v>
       </c>
       <c r="E21" t="n">
         <v>3.6558</v>
@@ -1422,7 +1422,7 @@
         <v>0.6969</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9923999999999999</v>
+        <v>0.9503</v>
       </c>
       <c r="E22" t="n">
         <v>3.4996</v>
@@ -1468,7 +1468,7 @@
         <v>0.6911</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9806</v>
+        <v>0.9387</v>
       </c>
       <c r="E23" t="n">
         <v>3.4704</v>
@@ -1514,7 +1514,7 @@
         <v>0.6661</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.8887</v>
       </c>
       <c r="E24" t="n">
         <v>3.3448</v>
@@ -1560,7 +1560,7 @@
         <v>0.5736</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7422</v>
+        <v>0.7036</v>
       </c>
       <c r="E25" t="n">
         <v>2.8802</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.6706</v>
+        <v>2.641</v>
       </c>
       <c r="C26" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5259</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6575</v>
+        <v>0.6083</v>
       </c>
       <c r="E26" t="n">
-        <v>2.6706</v>
+        <v>2.641</v>
       </c>
       <c r="F26" t="n">
-        <v>2.656</v>
+        <v>2.6264</v>
       </c>
       <c r="G26" t="n">
         <v>0.0146</v>
       </c>
       <c r="H26" t="n">
-        <v>2.656</v>
+        <v>2.6264</v>
       </c>
       <c r="I26" t="n">
         <v>2.6932</v>
@@ -1652,7 +1652,7 @@
         <v>0.4697</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5314</v>
+        <v>0.4957</v>
       </c>
       <c r="E27" t="n">
         <v>2.3585</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.2011</v>
+        <v>2.1891</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4383</v>
+        <v>0.4359</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4678</v>
+        <v>0.4282</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2011</v>
+        <v>2.1891</v>
       </c>
       <c r="F28" t="n">
-        <v>1.6091</v>
+        <v>1.5971</v>
       </c>
       <c r="G28" t="n">
         <v>0.592</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6091</v>
+        <v>1.5971</v>
       </c>
       <c r="I28" t="n">
         <v>1.6241</v>
@@ -1744,7 +1744,7 @@
         <v>0.4105</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4114</v>
+        <v>0.3773</v>
       </c>
       <c r="E29" t="n">
         <v>2.0613</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.0355</v>
+        <v>2.0078</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4054</v>
+        <v>0.3998</v>
       </c>
       <c r="D30" t="n">
-        <v>0.4009</v>
+        <v>0.356</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0355</v>
+        <v>2.0078</v>
       </c>
       <c r="F30" t="n">
-        <v>2.4879</v>
+        <v>2.4602</v>
       </c>
       <c r="G30" t="n">
         <v>-0.4524</v>
       </c>
       <c r="H30" t="n">
-        <v>2.4879</v>
+        <v>2.4602</v>
       </c>
       <c r="I30" t="n">
         <v>2.5228</v>
@@ -1836,7 +1836,7 @@
         <v>0.3502</v>
       </c>
       <c r="D31" t="n">
-        <v>0.289</v>
+        <v>0.2566</v>
       </c>
       <c r="E31" t="n">
         <v>1.7584</v>
@@ -1882,7 +1882,7 @@
         <v>0.3309</v>
       </c>
       <c r="D32" t="n">
-        <v>0.25</v>
+        <v>0.2182</v>
       </c>
       <c r="E32" t="n">
         <v>1.6618</v>
@@ -1928,7 +1928,7 @@
         <v>0.2548</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0956</v>
+        <v>0.0659</v>
       </c>
       <c r="E33" t="n">
         <v>1.2797</v>
@@ -1974,7 +1974,7 @@
         <v>0.2342</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0537</v>
+        <v>0.0246</v>
       </c>
       <c r="E34" t="n">
         <v>1.176</v>
@@ -2020,7 +2020,7 @@
         <v>0.1745</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.0673</v>
+        <v>-0.0948</v>
       </c>
       <c r="E35" t="n">
         <v>0.8764</v>
@@ -2066,7 +2066,7 @@
         <v>0.1621</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.0926</v>
+        <v>-0.1197</v>
       </c>
       <c r="E36" t="n">
         <v>0.8139</v>
@@ -2112,7 +2112,7 @@
         <v>0.1324</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.1528</v>
+        <v>-0.1791</v>
       </c>
       <c r="E37" t="n">
         <v>0.6647</v>
@@ -2158,7 +2158,7 @@
         <v>0.08840000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.242</v>
+        <v>-0.267</v>
       </c>
       <c r="E38" t="n">
         <v>0.4441</v>
@@ -2204,7 +2204,7 @@
         <v>0.0606</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.2985</v>
+        <v>-0.3228</v>
       </c>
       <c r="E39" t="n">
         <v>0.3041</v>
@@ -2250,7 +2250,7 @@
         <v>0.0372</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.3458</v>
+        <v>-0.3694</v>
       </c>
       <c r="E40" t="n">
         <v>0.187</v>
@@ -2296,7 +2296,7 @@
         <v>-0.0014</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.4243</v>
+        <v>-0.4468</v>
       </c>
       <c r="E41" t="n">
         <v>-0.0072</v>
@@ -2342,7 +2342,7 @@
         <v>-0.0544</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.5316</v>
+        <v>-0.5527</v>
       </c>
       <c r="E42" t="n">
         <v>-0.273</v>
@@ -2388,7 +2388,7 @@
         <v>-0.1198</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.6644</v>
+        <v>-0.6836</v>
       </c>
       <c r="E43" t="n">
         <v>-0.6017</v>
@@ -2434,7 +2434,7 @@
         <v>-0.1309</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.6869</v>
+        <v>-0.7058</v>
       </c>
       <c r="E44" t="n">
         <v>-0.6574</v>
@@ -2480,7 +2480,7 @@
         <v>-0.1846</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.8133</v>
       </c>
       <c r="E45" t="n">
         <v>-0.9271</v>
@@ -2526,7 +2526,7 @@
         <v>-0.1923</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.8114</v>
+        <v>-0.8286</v>
       </c>
       <c r="E46" t="n">
         <v>-0.9656</v>
@@ -2572,7 +2572,7 @@
         <v>-0.23</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.8878</v>
+        <v>-0.9039</v>
       </c>
       <c r="E47" t="n">
         <v>-1.1547</v>
@@ -2618,7 +2618,7 @@
         <v>-0.2653</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.9595</v>
+        <v>-0.9746</v>
       </c>
       <c r="E48" t="n">
         <v>-1.3321</v>
@@ -2664,7 +2664,7 @@
         <v>-0.2751</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.9792999999999999</v>
+        <v>-0.9942</v>
       </c>
       <c r="E49" t="n">
         <v>-1.3812</v>
@@ -2710,7 +2710,7 @@
         <v>-0.3006</v>
       </c>
       <c r="D50" t="n">
-        <v>-1.0312</v>
+        <v>-1.0453</v>
       </c>
       <c r="E50" t="n">
         <v>-1.5095</v>
@@ -2756,7 +2756,7 @@
         <v>-0.3723</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.1766</v>
+        <v>-1.1888</v>
       </c>
       <c r="E51" t="n">
         <v>-1.8696</v>
@@ -2802,7 +2802,7 @@
         <v>-0.4887</v>
       </c>
       <c r="D52" t="n">
-        <v>-1.4128</v>
+        <v>-1.4217</v>
       </c>
       <c r="E52" t="n">
         <v>-2.4542</v>
@@ -2848,7 +2848,7 @@
         <v>-0.4956</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.4267</v>
+        <v>-1.4354</v>
       </c>
       <c r="E53" t="n">
         <v>-2.4886</v>
@@ -2894,7 +2894,7 @@
         <v>-0.5299</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.4963</v>
+        <v>-1.5041</v>
       </c>
       <c r="E54" t="n">
         <v>-2.661</v>
@@ -2940,7 +2940,7 @@
         <v>-0.55</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.5371</v>
+        <v>-1.5442</v>
       </c>
       <c r="E55" t="n">
         <v>-2.7618</v>
@@ -2986,7 +2986,7 @@
         <v>-0.5749</v>
       </c>
       <c r="D56" t="n">
-        <v>-1.5876</v>
+        <v>-1.5941</v>
       </c>
       <c r="E56" t="n">
         <v>-2.8869</v>
@@ -3032,7 +3032,7 @@
         <v>-0.6147</v>
       </c>
       <c r="D57" t="n">
-        <v>-1.6684</v>
+        <v>-1.6737</v>
       </c>
       <c r="E57" t="n">
         <v>-3.0868</v>
@@ -3072,25 +3072,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-3.4014</v>
+        <v>-3.3795</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.6774</v>
+        <v>-0.673</v>
       </c>
       <c r="D58" t="n">
-        <v>-1.7955</v>
+        <v>-1.7903</v>
       </c>
       <c r="E58" t="n">
-        <v>-3.4014</v>
+        <v>-3.3795</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.9375</v>
+        <v>-2.9156</v>
       </c>
       <c r="G58" t="n">
         <v>-0.4639</v>
       </c>
       <c r="H58" t="n">
-        <v>-2.9375</v>
+        <v>-2.9156</v>
       </c>
       <c r="I58" t="n">
         <v>-2.9649</v>
@@ -3114,93 +3114,93 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>f4stzin</t>
+          <t>ryann</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-3.6094</v>
+        <v>-3.5945</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.7188</v>
+        <v>-0.7158</v>
       </c>
       <c r="D59" t="n">
-        <v>-1.8795</v>
+        <v>-1.876</v>
       </c>
       <c r="E59" t="n">
-        <v>-3.6094</v>
+        <v>-3.5945</v>
       </c>
       <c r="F59" t="n">
-        <v>-3.6094</v>
+        <v>-2.5945</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H59" t="n">
-        <v>-3.6094</v>
+        <v>-2.5945</v>
       </c>
       <c r="I59" t="n">
-        <v>-3.6094</v>
+        <v>-2.6606</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K59" t="n">
-        <v>282</v>
+        <v>434</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="M59" t="n">
-        <v>-3.6094</v>
+        <v>-3.6606</v>
       </c>
       <c r="N59" t="n">
-        <v>282</v>
+        <v>520</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ryann</t>
+          <t>f4stzin</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-3.6238</v>
+        <v>-3.6094</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.7217</v>
+        <v>-0.7188</v>
       </c>
       <c r="D60" t="n">
-        <v>-1.8853</v>
+        <v>-1.8819</v>
       </c>
       <c r="E60" t="n">
-        <v>-3.6238</v>
+        <v>-3.6094</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.6238</v>
+        <v>-3.6094</v>
       </c>
       <c r="G60" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-2.6238</v>
+        <v>-3.6094</v>
       </c>
       <c r="I60" t="n">
-        <v>-2.6606</v>
+        <v>-3.6094</v>
       </c>
       <c r="J60" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>434</v>
+        <v>282</v>
       </c>
       <c r="L60" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-3.6606</v>
+        <v>-3.6094</v>
       </c>
       <c r="N60" t="n">
-        <v>520</v>
+        <v>282</v>
       </c>
     </row>
     <row r="61">
@@ -3216,7 +3216,7 @@
         <v>-0.7689</v>
       </c>
       <c r="D61" t="n">
-        <v>-1.9812</v>
+        <v>-1.9822</v>
       </c>
       <c r="E61" t="n">
         <v>-3.8611</v>
